--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742774</v>
       </c>
       <c r="B2" t="n">
-        <v>79741</v>
+        <v>79843</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742774</v>
       </c>
       <c r="B2" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742774</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742774</v>
       </c>
       <c r="B2" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,907 @@
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128366427</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>730703</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7119237</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128366413</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>730697</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7119377</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128366424</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>730703</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7119279</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128366419</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>730676</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7119271</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128366418</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>730747</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7119204</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128366428</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>730661</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7119334</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128366425</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>730700</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7119383</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128366421</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80134</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>730751</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7119213</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128366429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80169</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>730755</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7119215</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1680,6 +1680,1471 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128384270</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>730661</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7119459</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128384278</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98393</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>730698</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7119431</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128384248</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>730625</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7119625</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128384256</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>730716</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7119393</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128384240</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>730618</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7119596</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128384246</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80164</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>730689</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7119410</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128384269</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>730721</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7119380</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128384250</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>730608</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7119552</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128384277</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98393</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>730689</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7119419</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128384253</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>730697</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7119408</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128384271</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>730613</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7119628</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128384272</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>730619</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7119597</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128384274</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>730603</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7119553</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128384247</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>730725</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7119407</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128384273</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Torpet, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>730609</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7119574</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128366427</v>
       </c>
       <c r="B3" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128366413</v>
       </c>
       <c r="B4" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128366424</v>
       </c>
       <c r="B5" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128366419</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,38 +1194,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R7" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,11 +1254,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1289,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B8" t="n">
-        <v>79031</v>
+        <v>57673</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,34 +1291,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R8" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,6 +1355,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1389,7 @@
         <v>128366425</v>
       </c>
       <c r="B9" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128366421</v>
       </c>
       <c r="B10" t="n">
-        <v>80134</v>
+        <v>80135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>128366429</v>
       </c>
       <c r="B11" t="n">
-        <v>80169</v>
+        <v>80170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,32 +1682,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128384270</v>
+        <v>128384278</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>98395</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730661</v>
+        <v>730698</v>
       </c>
       <c r="R12" t="n">
-        <v>7119459</v>
+        <v>7119431</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1779,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128384278</v>
+        <v>128384270</v>
       </c>
       <c r="B13" t="n">
-        <v>98393</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730698</v>
+        <v>730661</v>
       </c>
       <c r="R13" t="n">
-        <v>7119431</v>
+        <v>7119459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,27 +1876,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128384248</v>
+        <v>128384256</v>
       </c>
       <c r="B14" t="n">
-        <v>57670</v>
+        <v>58043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730625</v>
+        <v>730716</v>
       </c>
       <c r="R14" t="n">
-        <v>7119625</v>
+        <v>7119393</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,27 +1973,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128384256</v>
+        <v>128384248</v>
       </c>
       <c r="B15" t="n">
-        <v>58043</v>
+        <v>57670</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730716</v>
+        <v>730625</v>
       </c>
       <c r="R15" t="n">
-        <v>7119393</v>
+        <v>7119625</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,32 +2172,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128384246</v>
+        <v>128384269</v>
       </c>
       <c r="B17" t="n">
-        <v>80164</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730689</v>
+        <v>730721</v>
       </c>
       <c r="R17" t="n">
-        <v>7119410</v>
+        <v>7119380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,39 +2262,39 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128384269</v>
+        <v>128384246</v>
       </c>
       <c r="B18" t="n">
-        <v>79032</v>
+        <v>80164</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730721</v>
+        <v>730689</v>
       </c>
       <c r="R18" t="n">
-        <v>7119380</v>
+        <v>7119410</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2471,7 +2471,7 @@
         <v>128384277</v>
       </c>
       <c r="B20" t="n">
-        <v>98393</v>
+        <v>98395</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128384271</v>
+        <v>128384272</v>
       </c>
       <c r="B22" t="n">
         <v>79032</v>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730613</v>
+        <v>730619</v>
       </c>
       <c r="R22" t="n">
-        <v>7119628</v>
+        <v>7119597</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128384272</v>
+        <v>128384271</v>
       </c>
       <c r="B23" t="n">
         <v>79032</v>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730619</v>
+        <v>730613</v>
       </c>
       <c r="R23" t="n">
-        <v>7119597</v>
+        <v>7119628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,34 +1194,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R7" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1254,6 +1258,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B8" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,38 +1300,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R8" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,11 +1360,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128366427</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128366413</v>
       </c>
       <c r="B4" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128366424</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128366419</v>
       </c>
       <c r="B6" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,38 +1194,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R7" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,11 +1254,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1289,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,34 +1291,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R8" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,6 +1355,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1389,7 @@
         <v>128366425</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128366421</v>
       </c>
       <c r="B10" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>128366429</v>
       </c>
       <c r="B11" t="n">
-        <v>80170</v>
+        <v>80223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,32 +1682,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128384278</v>
+        <v>128384270</v>
       </c>
       <c r="B12" t="n">
-        <v>98395</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730698</v>
+        <v>730661</v>
       </c>
       <c r="R12" t="n">
-        <v>7119431</v>
+        <v>7119459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1779,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128384270</v>
+        <v>128384278</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>98488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730661</v>
+        <v>730698</v>
       </c>
       <c r="R13" t="n">
-        <v>7119459</v>
+        <v>7119431</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,27 +1876,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128384256</v>
+        <v>128384248</v>
       </c>
       <c r="B14" t="n">
-        <v>58043</v>
+        <v>57682</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730716</v>
+        <v>730625</v>
       </c>
       <c r="R14" t="n">
-        <v>7119393</v>
+        <v>7119625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,27 +1973,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128384248</v>
+        <v>128384256</v>
       </c>
       <c r="B15" t="n">
-        <v>57670</v>
+        <v>58055</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730625</v>
+        <v>730716</v>
       </c>
       <c r="R15" t="n">
-        <v>7119625</v>
+        <v>7119393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
         <v>128384240</v>
       </c>
       <c r="B16" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,32 +2172,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128384269</v>
+        <v>128384246</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>80217</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730721</v>
+        <v>730689</v>
       </c>
       <c r="R17" t="n">
-        <v>7119380</v>
+        <v>7119410</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,39 +2262,39 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128384246</v>
+        <v>128384269</v>
       </c>
       <c r="B18" t="n">
-        <v>80164</v>
+        <v>79083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730689</v>
+        <v>730721</v>
       </c>
       <c r="R18" t="n">
-        <v>7119410</v>
+        <v>7119380</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2369,7 +2369,7 @@
         <v>128384250</v>
       </c>
       <c r="B19" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>128384277</v>
       </c>
       <c r="B20" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>128384253</v>
       </c>
       <c r="B21" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128384272</v>
+        <v>128384271</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730619</v>
+        <v>730613</v>
       </c>
       <c r="R22" t="n">
-        <v>7119597</v>
+        <v>7119628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2759,10 +2759,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128384271</v>
+        <v>128384272</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730613</v>
+        <v>730619</v>
       </c>
       <c r="R23" t="n">
-        <v>7119628</v>
+        <v>7119597</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,7 +2859,7 @@
         <v>128384274</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>128384247</v>
       </c>
       <c r="B25" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>128384273</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -1876,27 +1876,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128384248</v>
+        <v>128384256</v>
       </c>
       <c r="B14" t="n">
-        <v>57682</v>
+        <v>58055</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730625</v>
+        <v>730716</v>
       </c>
       <c r="R14" t="n">
-        <v>7119625</v>
+        <v>7119393</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,27 +1973,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128384256</v>
+        <v>128384248</v>
       </c>
       <c r="B15" t="n">
-        <v>58055</v>
+        <v>57682</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730716</v>
+        <v>730625</v>
       </c>
       <c r="R15" t="n">
-        <v>7119393</v>
+        <v>7119625</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,32 +2172,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128384246</v>
+        <v>128384269</v>
       </c>
       <c r="B17" t="n">
-        <v>80217</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730689</v>
+        <v>730721</v>
       </c>
       <c r="R17" t="n">
-        <v>7119410</v>
+        <v>7119380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,39 +2262,39 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128384269</v>
+        <v>128384246</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>80217</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730721</v>
+        <v>730689</v>
       </c>
       <c r="R18" t="n">
-        <v>7119380</v>
+        <v>7119410</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128384271</v>
+        <v>128384272</v>
       </c>
       <c r="B22" t="n">
         <v>79083</v>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730613</v>
+        <v>730619</v>
       </c>
       <c r="R22" t="n">
-        <v>7119628</v>
+        <v>7119597</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128384272</v>
+        <v>128384271</v>
       </c>
       <c r="B23" t="n">
         <v>79083</v>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730619</v>
+        <v>730613</v>
       </c>
       <c r="R23" t="n">
-        <v>7119597</v>
+        <v>7119628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,34 +1194,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R7" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1254,6 +1258,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,38 +1300,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R8" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,11 +1360,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1876,27 +1876,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128384256</v>
+        <v>128384248</v>
       </c>
       <c r="B14" t="n">
-        <v>58055</v>
+        <v>57682</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730716</v>
+        <v>730625</v>
       </c>
       <c r="R14" t="n">
-        <v>7119393</v>
+        <v>7119625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,27 +1973,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128384248</v>
+        <v>128384256</v>
       </c>
       <c r="B15" t="n">
-        <v>57682</v>
+        <v>58055</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730625</v>
+        <v>730716</v>
       </c>
       <c r="R15" t="n">
-        <v>7119625</v>
+        <v>7119393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,32 +2172,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128384269</v>
+        <v>128384246</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>80217</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730721</v>
+        <v>730689</v>
       </c>
       <c r="R17" t="n">
-        <v>7119380</v>
+        <v>7119410</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,39 +2262,39 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128384246</v>
+        <v>128384269</v>
       </c>
       <c r="B18" t="n">
-        <v>80217</v>
+        <v>79083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730689</v>
+        <v>730721</v>
       </c>
       <c r="R18" t="n">
-        <v>7119410</v>
+        <v>7119380</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128366427</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128366413</v>
       </c>
       <c r="B4" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128366424</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128366419</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128366418</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128366428</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128366425</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128366421</v>
       </c>
       <c r="B10" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>128366429</v>
       </c>
       <c r="B11" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,32 +1682,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128384270</v>
+        <v>128384278</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>98502</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730661</v>
+        <v>730698</v>
       </c>
       <c r="R12" t="n">
-        <v>7119459</v>
+        <v>7119431</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1779,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128384278</v>
+        <v>128384270</v>
       </c>
       <c r="B13" t="n">
-        <v>98488</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730698</v>
+        <v>730661</v>
       </c>
       <c r="R13" t="n">
-        <v>7119431</v>
+        <v>7119459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,27 +1876,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128384248</v>
+        <v>128384256</v>
       </c>
       <c r="B14" t="n">
-        <v>57682</v>
+        <v>58059</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730625</v>
+        <v>730716</v>
       </c>
       <c r="R14" t="n">
-        <v>7119625</v>
+        <v>7119393</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,27 +1973,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128384256</v>
+        <v>128384248</v>
       </c>
       <c r="B15" t="n">
-        <v>58055</v>
+        <v>57686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730716</v>
+        <v>730625</v>
       </c>
       <c r="R15" t="n">
-        <v>7119393</v>
+        <v>7119625</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
         <v>128384240</v>
       </c>
       <c r="B16" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,32 +2172,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128384246</v>
+        <v>128384269</v>
       </c>
       <c r="B17" t="n">
-        <v>80217</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730689</v>
+        <v>730721</v>
       </c>
       <c r="R17" t="n">
-        <v>7119410</v>
+        <v>7119380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,39 +2262,39 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128384269</v>
+        <v>128384246</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>80221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730721</v>
+        <v>730689</v>
       </c>
       <c r="R18" t="n">
-        <v>7119380</v>
+        <v>7119410</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2369,7 +2369,7 @@
         <v>128384250</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>128384277</v>
       </c>
       <c r="B20" t="n">
-        <v>98488</v>
+        <v>98502</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>128384253</v>
       </c>
       <c r="B21" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>128384272</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>128384271</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128384274</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>128384247</v>
       </c>
       <c r="B25" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>128384273</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -1876,27 +1876,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128384256</v>
+        <v>128384248</v>
       </c>
       <c r="B14" t="n">
-        <v>58059</v>
+        <v>57686</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730716</v>
+        <v>730625</v>
       </c>
       <c r="R14" t="n">
-        <v>7119393</v>
+        <v>7119625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,27 +1973,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128384248</v>
+        <v>128384256</v>
       </c>
       <c r="B15" t="n">
-        <v>57686</v>
+        <v>58059</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730625</v>
+        <v>730716</v>
       </c>
       <c r="R15" t="n">
-        <v>7119625</v>
+        <v>7119393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128366427</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128366424</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>128366428</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128366425</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128366421</v>
       </c>
       <c r="B10" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>128366429</v>
       </c>
       <c r="B11" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>128384278</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>128384270</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1876,27 +1876,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128384248</v>
+        <v>128384256</v>
       </c>
       <c r="B14" t="n">
-        <v>57686</v>
+        <v>58059</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730625</v>
+        <v>730716</v>
       </c>
       <c r="R14" t="n">
-        <v>7119625</v>
+        <v>7119393</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,27 +1973,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128384256</v>
+        <v>128384248</v>
       </c>
       <c r="B15" t="n">
-        <v>58059</v>
+        <v>57686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730716</v>
+        <v>730625</v>
       </c>
       <c r="R15" t="n">
-        <v>7119393</v>
+        <v>7119625</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,32 +2172,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128384269</v>
+        <v>128384246</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>80223</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730721</v>
+        <v>730689</v>
       </c>
       <c r="R17" t="n">
-        <v>7119380</v>
+        <v>7119410</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,39 +2262,39 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128384246</v>
+        <v>128384269</v>
       </c>
       <c r="B18" t="n">
-        <v>80221</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730689</v>
+        <v>730721</v>
       </c>
       <c r="R18" t="n">
-        <v>7119410</v>
+        <v>7119380</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2471,7 +2471,7 @@
         <v>128384277</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>98505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>128384253</v>
       </c>
       <c r="B21" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>128384272</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>128384271</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128384274</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>128384273</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>128366424</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,38 +1194,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R7" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,11 +1254,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1289,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,34 +1291,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R8" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,6 +1355,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1389,7 @@
         <v>128366425</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1682,32 +1682,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128384278</v>
+        <v>128384270</v>
       </c>
       <c r="B12" t="n">
-        <v>98505</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730698</v>
+        <v>730661</v>
       </c>
       <c r="R12" t="n">
-        <v>7119431</v>
+        <v>7119459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1779,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128384270</v>
+        <v>128384278</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>98508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730661</v>
+        <v>730698</v>
       </c>
       <c r="R13" t="n">
-        <v>7119459</v>
+        <v>7119431</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2471,7 +2471,7 @@
         <v>128384277</v>
       </c>
       <c r="B20" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -1682,32 +1682,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128384270</v>
+        <v>128384278</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>98508</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730661</v>
+        <v>730698</v>
       </c>
       <c r="R12" t="n">
-        <v>7119459</v>
+        <v>7119431</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1779,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128384278</v>
+        <v>128384270</v>
       </c>
       <c r="B13" t="n">
-        <v>98508</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730698</v>
+        <v>730661</v>
       </c>
       <c r="R13" t="n">
-        <v>7119431</v>
+        <v>7119459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>128366424</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,34 +1194,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R7" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1254,6 +1258,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,38 +1300,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R8" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,11 +1360,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1389,7 @@
         <v>128366425</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1682,32 +1682,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128384278</v>
+        <v>128384270</v>
       </c>
       <c r="B12" t="n">
-        <v>98508</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730698</v>
+        <v>730661</v>
       </c>
       <c r="R12" t="n">
-        <v>7119431</v>
+        <v>7119459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1779,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128384270</v>
+        <v>128384278</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>98509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730661</v>
+        <v>730698</v>
       </c>
       <c r="R13" t="n">
-        <v>7119459</v>
+        <v>7119431</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2172,32 +2172,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128384246</v>
+        <v>128384269</v>
       </c>
       <c r="B17" t="n">
-        <v>80223</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730689</v>
+        <v>730721</v>
       </c>
       <c r="R17" t="n">
-        <v>7119410</v>
+        <v>7119380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,39 +2262,39 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128384269</v>
+        <v>128384246</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>80223</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730721</v>
+        <v>730689</v>
       </c>
       <c r="R18" t="n">
-        <v>7119380</v>
+        <v>7119410</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2471,7 +2471,7 @@
         <v>128384277</v>
       </c>
       <c r="B20" t="n">
-        <v>98508</v>
+        <v>98509</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128384272</v>
+        <v>128384271</v>
       </c>
       <c r="B22" t="n">
         <v>79089</v>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730619</v>
+        <v>730613</v>
       </c>
       <c r="R22" t="n">
-        <v>7119597</v>
+        <v>7119628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128384271</v>
+        <v>128384272</v>
       </c>
       <c r="B23" t="n">
         <v>79089</v>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730613</v>
+        <v>730619</v>
       </c>
       <c r="R23" t="n">
-        <v>7119628</v>
+        <v>7119597</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,38 +1194,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R7" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,11 +1254,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1289,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,34 +1291,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R8" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,6 +1355,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1682,32 +1682,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128384270</v>
+        <v>128384278</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>98509</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730661</v>
+        <v>730698</v>
       </c>
       <c r="R12" t="n">
-        <v>7119459</v>
+        <v>7119431</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1779,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128384278</v>
+        <v>128384270</v>
       </c>
       <c r="B13" t="n">
-        <v>98509</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730698</v>
+        <v>730661</v>
       </c>
       <c r="R13" t="n">
-        <v>7119431</v>
+        <v>7119459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,27 +1876,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128384256</v>
+        <v>128384248</v>
       </c>
       <c r="B14" t="n">
-        <v>58059</v>
+        <v>57686</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730716</v>
+        <v>730625</v>
       </c>
       <c r="R14" t="n">
-        <v>7119393</v>
+        <v>7119625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,27 +1973,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128384248</v>
+        <v>128384256</v>
       </c>
       <c r="B15" t="n">
-        <v>57686</v>
+        <v>58059</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730625</v>
+        <v>730716</v>
       </c>
       <c r="R15" t="n">
-        <v>7119625</v>
+        <v>7119393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128366427</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128366413</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128366424</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>128366419</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,34 +1194,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R7" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1254,6 +1258,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,38 +1300,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R8" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,11 +1360,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1389,7 @@
         <v>128366425</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128366421</v>
       </c>
       <c r="B10" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>128366429</v>
       </c>
       <c r="B11" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,32 +1682,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128384278</v>
+        <v>128384270</v>
       </c>
       <c r="B12" t="n">
-        <v>98509</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730698</v>
+        <v>730661</v>
       </c>
       <c r="R12" t="n">
-        <v>7119431</v>
+        <v>7119459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1779,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128384270</v>
+        <v>128384278</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>98536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730661</v>
+        <v>730698</v>
       </c>
       <c r="R13" t="n">
-        <v>7119459</v>
+        <v>7119431</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
         <v>128384248</v>
       </c>
       <c r="B14" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>128384256</v>
       </c>
       <c r="B15" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>128384240</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>128384269</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>128384246</v>
       </c>
       <c r="B18" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>128384250</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>128384277</v>
       </c>
       <c r="B20" t="n">
-        <v>98509</v>
+        <v>98536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>128384253</v>
       </c>
       <c r="B21" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128384271</v>
+        <v>128384272</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730613</v>
+        <v>730619</v>
       </c>
       <c r="R22" t="n">
-        <v>7119628</v>
+        <v>7119597</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2759,10 +2759,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128384272</v>
+        <v>128384271</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730619</v>
+        <v>730613</v>
       </c>
       <c r="R23" t="n">
-        <v>7119597</v>
+        <v>7119628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2859,7 +2859,7 @@
         <v>128384274</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>128384247</v>
       </c>
       <c r="B25" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>128384273</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,38 +1194,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R7" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,11 +1254,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1289,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,34 +1291,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R8" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,6 +1355,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2172,32 +2172,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128384269</v>
+        <v>128384246</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>80250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730721</v>
+        <v>730689</v>
       </c>
       <c r="R17" t="n">
-        <v>7119380</v>
+        <v>7119410</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,39 +2262,39 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128384246</v>
+        <v>128384269</v>
       </c>
       <c r="B18" t="n">
-        <v>80250</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730689</v>
+        <v>730721</v>
       </c>
       <c r="R18" t="n">
-        <v>7119410</v>
+        <v>7119380</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128366427</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128366424</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>128366428</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128366425</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>128366421</v>
       </c>
       <c r="B10" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>128366429</v>
       </c>
       <c r="B11" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>128384270</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>128384278</v>
       </c>
       <c r="B13" t="n">
-        <v>98536</v>
+        <v>98549</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>128384246</v>
       </c>
       <c r="B17" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>128384269</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>128384277</v>
       </c>
       <c r="B20" t="n">
-        <v>98536</v>
+        <v>98549</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>128384253</v>
       </c>
       <c r="B21" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>128384272</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>128384271</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>128384274</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>128384273</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -1682,32 +1682,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128384270</v>
+        <v>128384278</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>98549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730661</v>
+        <v>730698</v>
       </c>
       <c r="R12" t="n">
-        <v>7119459</v>
+        <v>7119431</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1779,32 +1779,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128384278</v>
+        <v>128384270</v>
       </c>
       <c r="B13" t="n">
-        <v>98549</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730698</v>
+        <v>730661</v>
       </c>
       <c r="R13" t="n">
-        <v>7119431</v>
+        <v>7119459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128366427</v>
+        <v>128384270</v>
       </c>
       <c r="B3" t="n">
         <v>79120</v>
@@ -812,14 +812,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730703</v>
+        <v>730661</v>
       </c>
       <c r="R3" t="n">
-        <v>7119237</v>
+        <v>7119459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,57 +866,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128366413</v>
+        <v>128384278</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>98549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730697</v>
+        <v>730698</v>
       </c>
       <c r="R4" t="n">
-        <v>7119377</v>
+        <v>7119431</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,61 +963,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128366424</v>
+        <v>128384248</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>57713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730703</v>
+        <v>730625</v>
       </c>
       <c r="R5" t="n">
-        <v>7119279</v>
+        <v>7119625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1058,46 +1054,45 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128366419</v>
+        <v>128384256</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>58086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1106,20 +1101,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730676</v>
+        <v>730716</v>
       </c>
       <c r="R6" t="n">
-        <v>7119271</v>
+        <v>7119393</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1145,6 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1171,22 +1157,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128366428</v>
+        <v>128384240</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,34 +1180,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730661</v>
+        <v>730618</v>
       </c>
       <c r="R7" t="n">
-        <v>7119334</v>
+        <v>7119596</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,6 +1242,11 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1268,61 +1259,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128366418</v>
+        <v>128384246</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>80254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730747</v>
+        <v>730689</v>
       </c>
       <c r="R8" t="n">
-        <v>7119204</v>
+        <v>7119410</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,11 +1344,6 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1374,61 +1356,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128366425</v>
+        <v>128384269</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730700</v>
+        <v>730721</v>
       </c>
       <c r="R9" t="n">
-        <v>7119383</v>
+        <v>7119380</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,29 +1447,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128366421</v>
+        <v>128384250</v>
       </c>
       <c r="B10" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,34 +1476,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730751</v>
+        <v>730608</v>
       </c>
       <c r="R10" t="n">
-        <v>7119213</v>
+        <v>7119552</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,6 +1538,11 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1573,22 +1555,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128366429</v>
+        <v>128384277</v>
       </c>
       <c r="B11" t="n">
-        <v>80260</v>
+        <v>98549</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1596,34 +1578,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730755</v>
+        <v>730689</v>
       </c>
       <c r="R11" t="n">
-        <v>7119215</v>
+        <v>7119419</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1670,44 +1652,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128384278</v>
+        <v>128384253</v>
       </c>
       <c r="B12" t="n">
-        <v>98549</v>
+        <v>80225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730698</v>
+        <v>730697</v>
       </c>
       <c r="R12" t="n">
-        <v>7119431</v>
+        <v>7119408</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1772,14 +1754,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128384270</v>
+        <v>128384272</v>
       </c>
       <c r="B13" t="n">
         <v>79120</v>
@@ -1814,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730661</v>
+        <v>730619</v>
       </c>
       <c r="R13" t="n">
-        <v>7119459</v>
+        <v>7119597</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,10 +1858,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128384248</v>
+        <v>128384271</v>
       </c>
       <c r="B14" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,21 +1869,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1911,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730625</v>
+        <v>730613</v>
       </c>
       <c r="R14" t="n">
-        <v>7119625</v>
+        <v>7119628</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,39 +1948,39 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128384256</v>
+        <v>128384274</v>
       </c>
       <c r="B15" t="n">
-        <v>58086</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730716</v>
+        <v>730603</v>
       </c>
       <c r="R15" t="n">
-        <v>7119393</v>
+        <v>7119553</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,17 +2045,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128384240</v>
+        <v>128384247</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>57713</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,16 +2063,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2105,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730618</v>
+        <v>730725</v>
       </c>
       <c r="R16" t="n">
-        <v>7119596</v>
+        <v>7119407</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2141,11 +2123,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2172,32 +2149,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128384246</v>
+        <v>128384273</v>
       </c>
       <c r="B17" t="n">
-        <v>80254</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2184,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730689</v>
+        <v>730609</v>
       </c>
       <c r="R17" t="n">
-        <v>7119410</v>
+        <v>7119574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,14 +2239,14 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128384269</v>
+        <v>128366427</v>
       </c>
       <c r="B18" t="n">
         <v>79120</v>
@@ -2300,14 +2277,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730721</v>
+        <v>730703</v>
       </c>
       <c r="R18" t="n">
-        <v>7119380</v>
+        <v>7119237</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2354,22 +2331,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128384250</v>
+        <v>128366413</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>57876</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2377,34 +2354,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730608</v>
+        <v>730697</v>
       </c>
       <c r="R19" t="n">
-        <v>7119552</v>
+        <v>7119377</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2439,11 +2416,6 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2456,57 +2428,61 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128384277</v>
+        <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98549</v>
+        <v>98632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730689</v>
+        <v>730703</v>
       </c>
       <c r="R20" t="n">
-        <v>7119419</v>
+        <v>7119279</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,28 +2523,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128384253</v>
+        <v>128366419</v>
       </c>
       <c r="B21" t="n">
-        <v>80225</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2576,34 +2553,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730697</v>
+        <v>730676</v>
       </c>
       <c r="R21" t="n">
-        <v>7119408</v>
+        <v>7119271</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2638,6 +2619,11 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2650,22 +2636,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128384272</v>
+        <v>128366418</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2673,34 +2659,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730619</v>
+        <v>730747</v>
       </c>
       <c r="R22" t="n">
-        <v>7119597</v>
+        <v>7119204</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2735,6 +2725,11 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2747,19 +2742,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128384271</v>
+        <v>128366428</v>
       </c>
       <c r="B23" t="n">
         <v>79120</v>
@@ -2790,14 +2785,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730613</v>
+        <v>730661</v>
       </c>
       <c r="R23" t="n">
-        <v>7119628</v>
+        <v>7119334</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2844,57 +2839,61 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128384274</v>
+        <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>98632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730603</v>
+        <v>730700</v>
       </c>
       <c r="R24" t="n">
-        <v>7119553</v>
+        <v>7119383</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2935,28 +2934,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128384247</v>
+        <v>128366421</v>
       </c>
       <c r="B25" t="n">
-        <v>57713</v>
+        <v>80225</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2964,34 +2964,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730725</v>
+        <v>730751</v>
       </c>
       <c r="R25" t="n">
-        <v>7119407</v>
+        <v>7119213</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3038,39 +3038,39 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128384273</v>
+        <v>128366429</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>80260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3081,14 +3081,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730609</v>
+        <v>730755</v>
       </c>
       <c r="R26" t="n">
-        <v>7119574</v>
+        <v>7119215</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3135,12 +3135,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128384270</v>
+        <v>128384278</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>98549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730661</v>
+        <v>730698</v>
       </c>
       <c r="R3" t="n">
-        <v>7119459</v>
+        <v>7119431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,32 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128384278</v>
+        <v>128384270</v>
       </c>
       <c r="B4" t="n">
-        <v>98549</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730698</v>
+        <v>730661</v>
       </c>
       <c r="R4" t="n">
-        <v>7119431</v>
+        <v>7119459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1271,32 +1271,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384246</v>
+        <v>128384269</v>
       </c>
       <c r="B8" t="n">
-        <v>80254</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730689</v>
+        <v>730721</v>
       </c>
       <c r="R8" t="n">
-        <v>7119410</v>
+        <v>7119380</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,39 +1361,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128384269</v>
+        <v>128384246</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>80254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730721</v>
+        <v>730689</v>
       </c>
       <c r="R9" t="n">
-        <v>7119380</v>
+        <v>7119410</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128384272</v>
+        <v>128384271</v>
       </c>
       <c r="B13" t="n">
         <v>79120</v>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730619</v>
+        <v>730613</v>
       </c>
       <c r="R13" t="n">
-        <v>7119597</v>
+        <v>7119628</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128384271</v>
+        <v>128384272</v>
       </c>
       <c r="B14" t="n">
         <v>79120</v>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730613</v>
+        <v>730619</v>
       </c>
       <c r="R14" t="n">
-        <v>7119628</v>
+        <v>7119597</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2249,7 +2249,7 @@
         <v>128366427</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>128366413</v>
       </c>
       <c r="B19" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>128366419</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B22" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2659,38 +2659,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R22" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2723,11 +2719,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2754,10 +2745,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2765,34 +2756,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R23" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,6 +2820,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>128366421</v>
       </c>
       <c r="B25" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>128366429</v>
       </c>
       <c r="B26" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128384278</v>
       </c>
       <c r="B3" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128384270</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128384248</v>
       </c>
       <c r="B5" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128384256</v>
       </c>
       <c r="B6" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128384240</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128384269</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128384246</v>
       </c>
       <c r="B9" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128384250</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128384277</v>
       </c>
       <c r="B11" t="n">
-        <v>98549</v>
+        <v>98553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>128384253</v>
       </c>
       <c r="B12" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128384271</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>128384272</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>128384274</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>128384247</v>
       </c>
       <c r="B16" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>128384273</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128384278</v>
+        <v>128384270</v>
       </c>
       <c r="B3" t="n">
-        <v>98553</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730698</v>
+        <v>730661</v>
       </c>
       <c r="R3" t="n">
-        <v>7119431</v>
+        <v>7119459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,32 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128384270</v>
+        <v>128384278</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>98553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730661</v>
+        <v>730698</v>
       </c>
       <c r="R4" t="n">
-        <v>7119459</v>
+        <v>7119431</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1271,32 +1271,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384269</v>
+        <v>128384246</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>80258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730721</v>
+        <v>730689</v>
       </c>
       <c r="R8" t="n">
-        <v>7119380</v>
+        <v>7119410</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,39 +1361,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128384246</v>
+        <v>128384269</v>
       </c>
       <c r="B9" t="n">
-        <v>80258</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730689</v>
+        <v>730721</v>
       </c>
       <c r="R9" t="n">
-        <v>7119410</v>
+        <v>7119380</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128384270</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>128384278</v>
       </c>
       <c r="B4" t="n">
-        <v>98553</v>
+        <v>98560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>128384248</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>128384256</v>
       </c>
       <c r="B6" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>128384240</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>128384246</v>
       </c>
       <c r="B8" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>128384269</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>128384250</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128384277</v>
       </c>
       <c r="B11" t="n">
-        <v>98553</v>
+        <v>98560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>128384253</v>
       </c>
       <c r="B12" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128384271</v>
+        <v>128384272</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730613</v>
+        <v>730619</v>
       </c>
       <c r="R13" t="n">
-        <v>7119628</v>
+        <v>7119597</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,10 +1858,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128384272</v>
+        <v>128384271</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730619</v>
+        <v>730613</v>
       </c>
       <c r="R14" t="n">
-        <v>7119597</v>
+        <v>7119628</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,7 +1958,7 @@
         <v>128384274</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>128384247</v>
       </c>
       <c r="B16" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>128384273</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>128366427</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>128366413</v>
       </c>
       <c r="B19" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>128366419</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>128366428</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>128366418</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>128366421</v>
       </c>
       <c r="B25" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>128366429</v>
       </c>
       <c r="B26" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -2249,7 +2249,7 @@
         <v>128366427</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>128366428</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>128366421</v>
       </c>
       <c r="B25" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>128366429</v>
       </c>
       <c r="B26" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -2249,7 +2249,7 @@
         <v>128366427</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>128366413</v>
       </c>
       <c r="B19" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>128366419</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2659,34 +2659,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R22" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2719,6 +2723,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2745,10 +2754,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2756,38 +2765,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R23" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2820,11 +2825,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>128366421</v>
       </c>
       <c r="B25" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>128366429</v>
       </c>
       <c r="B26" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -2648,10 +2648,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2659,38 +2659,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R22" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2723,11 +2719,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2754,10 +2745,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2765,34 +2756,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R23" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,6 +2820,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -2249,7 +2249,7 @@
         <v>128366427</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2346,7 +2346,7 @@
         <v>128366413</v>
       </c>
       <c r="B19" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2545,7 +2545,7 @@
         <v>128366419</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
         <v>128366428</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2748,7 +2748,7 @@
         <v>128366418</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -2956,7 +2956,7 @@
         <v>128366421</v>
       </c>
       <c r="B25" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3053,7 +3053,7 @@
         <v>128366429</v>
       </c>
       <c r="B26" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2659,34 +2659,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R22" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2719,6 +2723,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2745,10 +2754,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2756,38 +2765,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R23" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2820,11 +2825,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2659,38 +2659,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R22" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2723,11 +2719,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2754,10 +2745,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2765,34 +2756,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R23" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,6 +2820,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -2249,7 +2249,7 @@
         <v>128366427</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>128366428</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>128366421</v>
       </c>
       <c r="B25" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>128366429</v>
       </c>
       <c r="B26" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -2249,7 +2249,7 @@
         <v>128366427</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2659,34 +2659,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R22" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2719,6 +2723,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2745,10 +2754,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2756,38 +2765,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R23" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2820,11 +2825,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>128366421</v>
       </c>
       <c r="B25" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>128366429</v>
       </c>
       <c r="B26" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2641,17 +2641,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2659,38 +2659,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R22" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2725,11 +2721,6 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2747,17 +2738,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2765,34 +2756,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R23" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2827,6 +2822,11 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
         <v>128366424</v>
       </c>
       <c r="B20" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2641,17 +2641,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128366428</v>
+        <v>128366418</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2659,34 +2659,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730661</v>
+        <v>730747</v>
       </c>
       <c r="R22" t="n">
-        <v>7119334</v>
+        <v>7119204</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,6 +2725,11 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2738,17 +2747,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128366418</v>
+        <v>128366428</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2756,38 +2765,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730747</v>
+        <v>730661</v>
       </c>
       <c r="R23" t="n">
-        <v>7119204</v>
+        <v>7119334</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2822,11 +2827,6 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2854,7 +2854,7 @@
         <v>128366425</v>
       </c>
       <c r="B24" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742774</v>
       </c>
       <c r="B2" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742774</v>
       </c>
       <c r="B2" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742774</v>
       </c>
       <c r="B2" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742774</v>
       </c>
       <c r="B2" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742774</v>
       </c>
       <c r="B2" t="n">
-        <v>80433</v>
+        <v>80434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742774</v>
+        <v>128366427</v>
       </c>
       <c r="B2" t="n">
-        <v>80437</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långtj. NV, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730693</v>
+        <v>730703</v>
       </c>
       <c r="R2" t="n">
-        <v>7119413</v>
+        <v>7119237</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,30 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128384270</v>
+        <v>128366428</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>730661</v>
       </c>
       <c r="R3" t="n">
-        <v>7119459</v>
+        <v>7119334</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,44 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128384278</v>
+        <v>128384269</v>
       </c>
       <c r="B4" t="n">
-        <v>98560</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730698</v>
+        <v>730721</v>
       </c>
       <c r="R4" t="n">
-        <v>7119431</v>
+        <v>7119380</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128384248</v>
+        <v>128384270</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730625</v>
+        <v>730661</v>
       </c>
       <c r="R5" t="n">
-        <v>7119625</v>
+        <v>7119459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1060,39 +1056,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128384256</v>
+        <v>128384271</v>
       </c>
       <c r="B6" t="n">
-        <v>58093</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730716</v>
+        <v>730613</v>
       </c>
       <c r="R6" t="n">
-        <v>7119393</v>
+        <v>7119628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,39 +1153,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128384240</v>
+        <v>128384272</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730618</v>
+        <v>730619</v>
       </c>
       <c r="R7" t="n">
-        <v>7119596</v>
+        <v>7119597</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,11 +1233,6 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1259,39 +1250,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384246</v>
+        <v>128384273</v>
       </c>
       <c r="B8" t="n">
-        <v>80163</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730689</v>
+        <v>730609</v>
       </c>
       <c r="R8" t="n">
-        <v>7119410</v>
+        <v>7119574</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1356,21 +1347,21 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128384269</v>
+        <v>128384274</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1398,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730721</v>
+        <v>730603</v>
       </c>
       <c r="R9" t="n">
-        <v>7119380</v>
+        <v>7119553</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128384250</v>
+        <v>122742774</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>80488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Långtj. NV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730608</v>
+        <v>730693</v>
       </c>
       <c r="R10" t="n">
-        <v>7119552</v>
+        <v>7119413</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1525,17 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1550,57 +1536,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128384277</v>
+        <v>128366421</v>
       </c>
       <c r="B11" t="n">
-        <v>98560</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730689</v>
+        <v>730751</v>
       </c>
       <c r="R11" t="n">
-        <v>7119419</v>
+        <v>7119213</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,12 +1637,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1662,7 +1652,7 @@
         <v>128384253</v>
       </c>
       <c r="B12" t="n">
-        <v>80134</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,32 +1746,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128384272</v>
+        <v>128384246</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1791,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730619</v>
+        <v>730689</v>
       </c>
       <c r="R13" t="n">
-        <v>7119597</v>
+        <v>7119410</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1846,34 +1836,34 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128384271</v>
+        <v>128366429</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>80467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1884,14 +1874,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730613</v>
+        <v>730755</v>
       </c>
       <c r="R14" t="n">
-        <v>7119628</v>
+        <v>7119215</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1938,44 +1928,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128384274</v>
+        <v>128384247</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1985,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730603</v>
+        <v>730725</v>
       </c>
       <c r="R15" t="n">
-        <v>7119553</v>
+        <v>7119407</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,21 +2030,21 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128384247</v>
+        <v>128384248</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2082,10 +2072,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730725</v>
+        <v>730625</v>
       </c>
       <c r="R16" t="n">
-        <v>7119407</v>
+        <v>7119625</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,10 +2134,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128384273</v>
+        <v>128366418</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2155,34 +2145,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Torpet, Vb</t>
+          <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730609</v>
+        <v>730747</v>
       </c>
       <c r="R17" t="n">
-        <v>7119574</v>
+        <v>7119204</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2217,6 +2211,11 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2229,22 +2228,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128366427</v>
+        <v>128366419</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2252,34 +2251,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730703</v>
+        <v>730676</v>
       </c>
       <c r="R18" t="n">
-        <v>7119237</v>
+        <v>7119271</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2312,6 +2315,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2338,10 +2346,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128366413</v>
+        <v>128384240</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,34 +2357,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730697</v>
+        <v>730618</v>
       </c>
       <c r="R19" t="n">
-        <v>7119377</v>
+        <v>7119596</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2411,6 +2419,11 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2423,61 +2436,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128366424</v>
+        <v>128384250</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730703</v>
+        <v>730608</v>
       </c>
       <c r="R20" t="n">
-        <v>7119279</v>
+        <v>7119552</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2512,52 +2521,56 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128366419</v>
+        <v>128384256</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>58327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2566,20 +2579,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730676</v>
+        <v>730716</v>
       </c>
       <c r="R21" t="n">
-        <v>7119271</v>
+        <v>7119393</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,11 +2623,6 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2631,22 +2635,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128366418</v>
+        <v>128366413</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2654,38 +2658,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730747</v>
+        <v>730697</v>
       </c>
       <c r="R22" t="n">
-        <v>7119204</v>
+        <v>7119377</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2718,11 +2718,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2749,45 +2744,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128366428</v>
+        <v>128384277</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>99035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730661</v>
+        <v>730689</v>
       </c>
       <c r="R23" t="n">
-        <v>7119334</v>
+        <v>7119419</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2834,61 +2829,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128366425</v>
+        <v>128384278</v>
       </c>
       <c r="B24" t="n">
-        <v>98724</v>
+        <v>99035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Torpet, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730700</v>
+        <v>730698</v>
       </c>
       <c r="R24" t="n">
-        <v>7119383</v>
+        <v>7119431</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2929,64 +2920,63 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128366421</v>
+        <v>122742798</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sanddalsmyran, Vb</t>
+          <t>Tvärtförberget SÖ, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730751</v>
+        <v>730764</v>
       </c>
       <c r="R25" t="n">
-        <v>7119213</v>
+        <v>7119395</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3013,12 +3003,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3033,57 +3023,65 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128366429</v>
+        <v>128366424</v>
       </c>
       <c r="B26" t="n">
-        <v>80184</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sanddalsmyran, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730755</v>
+        <v>730703</v>
       </c>
       <c r="R26" t="n">
-        <v>7119215</v>
+        <v>7119279</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3124,6 +3122,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3139,6 +3138,108 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128366425</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sanddalsmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>730700</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7119383</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28716-2024 artfynd.xlsx
+++ b/artfynd/A 28716-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366427</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366428</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384269</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384270</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384271</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384272</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384273</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384274</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122742774</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366421</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384253</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384246</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366429</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384247</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384248</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2237,6 +2317,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366418</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2343,6 +2428,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366419</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2445,6 +2535,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384240</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2547,6 +2642,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384250</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2644,6 +2744,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384256</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2741,6 +2846,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366413</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2838,6 +2948,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384277</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2935,6 +3050,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384278</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3034,6 +3154,11 @@
       <c r="AY25" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122742798</t>
         </is>
       </c>
     </row>
@@ -3138,6 +3263,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366424</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3240,8 +3370,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128366425</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>